--- a/docs/MUSCLE_EXPERIENCE_CONDITIONING_PROPOSED_2026-08-05.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_CONDITIONING_PROPOSED_2026-08-05.xlsx
@@ -8,7 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conditioning 53 PROPOSED" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Modality Muscle Map" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="READ ME" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -38,8 +39,13 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -56,6 +62,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -69,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -88,6 +99,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -468,32 +491,32 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="8" t="inlineStr">
         <is>
           <t>Exercise</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="8" t="inlineStr">
         <is>
           <t>Quality tab</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="8" t="inlineStr">
         <is>
           <t>Pool</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Primary muscle groups</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Secondary muscle groups</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Experience gate</t>
         </is>
@@ -503,36 +526,44 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="8" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" s="8" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="9" t="inlineStr">
         <is>
           <t>10 m Acceleration Reps</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr"/>
-      <c r="E2" s="4" t="inlineStr"/>
-      <c r="F2" s="4" t="inlineStr">
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F2" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -542,36 +573,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="H2" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I2" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="9" t="inlineStr">
         <is>
           <t>20 m Acceleration Reps</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr"/>
-      <c r="E3" s="4" t="inlineStr"/>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="C3" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D3" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E3" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F3" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -581,36 +620,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I3" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>30 m Acceleration Reps</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr"/>
-      <c r="E4" s="4" t="inlineStr"/>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -620,36 +667,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I4" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Air Bike Accelerations</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
@@ -659,32 +714,40 @@
           <t>machine modality — no field sprint mechanics.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr"/>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="H5" s="9" t="inlineStr"/>
+      <c r="I5" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Hill Acceleration</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr"/>
-      <c r="E6" s="4" t="inlineStr"/>
-      <c r="F6" s="4" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F6" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -694,36 +757,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I6" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Return-to-Speed Ladder</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="4" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E7" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F7" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -733,36 +804,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I7" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I7" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Team-Training Warm-Up Dose</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>acceleration</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr"/>
-      <c r="E8" s="4" t="inlineStr"/>
-      <c r="F8" s="4" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Glutes, Quads, Calves</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Hips</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
@@ -772,32 +851,40 @@
           <t>warm-up dose ridden onto a team night — never a standalone session (ruling 5, 2026-08-05).</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr"/>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="H8" s="9" t="inlineStr"/>
+      <c r="I8" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Fly 20 (20+20)</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>top_end_speed</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
-      <c r="F9" s="4" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes</t>
+        </is>
+      </c>
+      <c r="E9" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hips, Quads</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -807,36 +894,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I9" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Fly 30 (30+30)</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>top_end_speed</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr"/>
-      <c r="E10" s="4" t="inlineStr"/>
-      <c r="F10" s="4" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes</t>
+        </is>
+      </c>
+      <c r="E10" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hips, Quads</t>
+        </is>
+      </c>
+      <c r="F10" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -846,36 +941,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I10" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Off-Season Speed Reintroduction</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>top_end_speed</t>
         </is>
       </c>
-      <c r="C11" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr"/>
-      <c r="E11" s="4" t="inlineStr"/>
-      <c r="F11" s="4" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D11" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes</t>
+        </is>
+      </c>
+      <c r="E11" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hips, Quads</t>
+        </is>
+      </c>
+      <c r="F11" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -885,36 +988,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I11" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Progressive Sprint Exposure</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>top_end_speed</t>
         </is>
       </c>
-      <c r="C12" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D12" s="4" t="inlineStr"/>
-      <c r="E12" s="4" t="inlineStr"/>
-      <c r="F12" s="4" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D12" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes</t>
+        </is>
+      </c>
+      <c r="E12" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hips, Quads</t>
+        </is>
+      </c>
+      <c r="F12" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -924,106 +1035,130 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H12" s="3" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>10 s Max Sprint Repeats</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>repeat_sprint</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr"/>
-      <c r="E13" s="4" t="inlineStr"/>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D13" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F13" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>machine/erg rendering — no field sprint mechanics.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr"/>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>machine/erg rendering — no field sprint mechanics. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H13" s="9" t="inlineStr"/>
+      <c r="I13" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>10 s Repeat Efforts</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="9" t="inlineStr">
         <is>
           <t>repeat_sprint</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr"/>
-      <c r="E14" s="4" t="inlineStr"/>
-      <c r="F14" s="4" t="inlineStr">
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>machine/erg rendering — no field sprint mechanics.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="inlineStr"/>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>machine/erg rendering — no field sprint mechanics. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H14" s="9" t="inlineStr"/>
+      <c r="I14" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>20 m Shuttle Repeats</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B15" s="9" t="inlineStr">
         <is>
           <t>repeat_sprint</t>
         </is>
       </c>
-      <c r="C15" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D15" s="4" t="inlineStr"/>
-      <c r="E15" s="4" t="inlineStr"/>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D15" s="10" t="inlineStr">
+        <is>
+          <t>Hamstrings, Glutes, Quads</t>
+        </is>
+      </c>
+      <c r="E15" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hips</t>
+        </is>
+      </c>
+      <c r="F15" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1033,106 +1168,130 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H15" s="3" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I15" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I15" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>30 m Repeats</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="9" t="inlineStr">
         <is>
           <t>repeat_sprint</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr"/>
-      <c r="E16" s="4" t="inlineStr"/>
-      <c r="F16" s="4" t="inlineStr">
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F16" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>machine/erg rendering — no field sprint mechanics.</t>
-        </is>
-      </c>
-      <c r="H16" s="3" t="inlineStr"/>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>machine/erg rendering — no field sprint mechanics. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H16" s="9" t="inlineStr"/>
+      <c r="I16" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Sprint Sets (3×5×6 s)</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="9" t="inlineStr">
         <is>
           <t>repeat_sprint</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr"/>
-      <c r="E17" s="4" t="inlineStr"/>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F17" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>machine/erg rendering — no field sprint mechanics.</t>
-        </is>
-      </c>
-      <c r="H17" s="3" t="inlineStr"/>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>machine/erg rendering — no field sprint mechanics. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H17" s="9" t="inlineStr"/>
+      <c r="I17" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>45-Degree Cut Reps</t>
         </is>
       </c>
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="9" t="inlineStr">
         <is>
           <t>cod_decel</t>
         </is>
       </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D18" s="4" t="inlineStr"/>
-      <c r="E18" s="4" t="inlineStr"/>
-      <c r="F18" s="4" t="inlineStr">
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Groin</t>
+        </is>
+      </c>
+      <c r="E18" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hamstrings, Knee</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1142,36 +1301,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H18" s="3" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I18" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>Deceleration and Landing Work</t>
         </is>
       </c>
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>cod_decel</t>
         </is>
       </c>
-      <c r="C19" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr"/>
-      <c r="E19" s="4" t="inlineStr"/>
-      <c r="F19" s="4" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D19" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes</t>
+        </is>
+      </c>
+      <c r="E19" s="10" t="inlineStr">
+        <is>
+          <t>Knee, Calves, Hamstrings</t>
+        </is>
+      </c>
+      <c r="F19" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
@@ -1181,32 +1348,40 @@
           <t>low-intensity mechanics / landing work — teachable to everyone.</t>
         </is>
       </c>
-      <c r="H19" s="3" t="inlineStr"/>
-      <c r="I19" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="H19" s="9" t="inlineStr"/>
+      <c r="I19" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>Low-Intensity Deceleration Drills</t>
         </is>
       </c>
-      <c r="B20" s="3" t="inlineStr">
+      <c r="B20" s="9" t="inlineStr">
         <is>
           <t>cod_decel</t>
         </is>
       </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr"/>
-      <c r="E20" s="4" t="inlineStr"/>
-      <c r="F20" s="4" t="inlineStr">
+      <c r="C20" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D20" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes</t>
+        </is>
+      </c>
+      <c r="E20" s="10" t="inlineStr">
+        <is>
+          <t>Knee, Calves, Hamstrings</t>
+        </is>
+      </c>
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
@@ -1216,32 +1391,40 @@
           <t>low-intensity mechanics / landing work — teachable to everyone.</t>
         </is>
       </c>
-      <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="H20" s="9" t="inlineStr"/>
+      <c r="I20" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>Up-Back Shuttle</t>
         </is>
       </c>
-      <c r="B21" s="3" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>cod_decel</t>
         </is>
       </c>
-      <c r="C21" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr"/>
-      <c r="E21" s="4" t="inlineStr"/>
-      <c r="F21" s="4" t="inlineStr">
+      <c r="C21" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Groin</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Hamstrings, Knee</t>
+        </is>
+      </c>
+      <c r="F21" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1251,36 +1434,44 @@
           <t>⚑ field sprint/cutting mechanics. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="inlineStr">
+      <c r="H21" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I21" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I21" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>150–200 m Hard Repeats</t>
         </is>
       </c>
-      <c r="B22" s="3" t="inlineStr">
+      <c r="B22" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C22" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D22" s="4" t="inlineStr"/>
-      <c r="E22" s="4" t="inlineStr"/>
-      <c r="F22" s="4" t="inlineStr">
+      <c r="C22" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F22" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1290,36 +1481,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H22" s="3" t="inlineStr">
+      <c r="H22" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I22" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I22" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>20 s Max Sprint — Small Dose</t>
         </is>
       </c>
-      <c r="B23" s="3" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr"/>
-      <c r="E23" s="4" t="inlineStr"/>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E23" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1329,106 +1528,130 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H23" s="3" t="inlineStr">
+      <c r="H23" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>30 s Very Hard Repeats</t>
         </is>
       </c>
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C24" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D24" s="4" t="inlineStr"/>
-      <c r="E24" s="4" t="inlineStr"/>
-      <c r="F24" s="4" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F24" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H24" s="3" t="inlineStr"/>
-      <c r="I24" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H24" s="9" t="inlineStr"/>
+      <c r="I24" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>45 s Hard Repeats</t>
         </is>
       </c>
-      <c r="B25" s="3" t="inlineStr">
+      <c r="B25" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr"/>
-      <c r="E25" s="4" t="inlineStr"/>
-      <c r="F25" s="4" t="inlineStr">
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F25" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H25" s="3" t="inlineStr"/>
-      <c r="I25" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr"/>
+      <c r="I25" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>60 s Max Sustained Effort</t>
         </is>
       </c>
-      <c r="B26" s="3" t="inlineStr">
+      <c r="B26" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D26" s="4" t="inlineStr"/>
-      <c r="E26" s="4" t="inlineStr"/>
-      <c r="F26" s="4" t="inlineStr">
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F26" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1438,71 +1661,87 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H26" s="3" t="inlineStr">
+      <c r="H26" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I26" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I26" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>Bodyweight Circuit (no-equipment fallback)</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D27" s="4" t="inlineStr"/>
-      <c r="E27" s="4" t="inlineStr"/>
-      <c r="F27" s="4" t="inlineStr">
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>session format, not an individual movement — no meaningful muscle group.</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr"/>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>session format, not an individual movement — no meaningful muscle group. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H27" s="9" t="inlineStr"/>
+      <c r="I27" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>Erg Short-Burst Repeats (15–20 s)</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B28" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D28" s="4" t="inlineStr"/>
-      <c r="E28" s="4" t="inlineStr"/>
-      <c r="F28" s="4" t="inlineStr">
+      <c r="C28" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E28" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F28" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
@@ -1512,32 +1751,40 @@
           <t>machine modality — no field sprint mechanics.</t>
         </is>
       </c>
-      <c r="H28" s="3" t="inlineStr"/>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="H28" s="9" t="inlineStr"/>
+      <c r="I28" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>Hill Repeats — hard sustained</t>
         </is>
       </c>
-      <c r="B29" s="3" t="inlineStr">
+      <c r="B29" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C29" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr"/>
-      <c r="E29" s="4" t="inlineStr"/>
-      <c r="F29" s="4" t="inlineStr">
+      <c r="C29" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D29" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E29" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F29" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1547,36 +1794,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H29" s="3" t="inlineStr">
+      <c r="H29" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I29" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>Tabata Finisher</t>
         </is>
       </c>
-      <c r="B30" s="3" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>anaerobic</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D30" s="4" t="inlineStr"/>
-      <c r="E30" s="4" t="inlineStr"/>
-      <c r="F30" s="4" t="inlineStr">
+      <c r="C30" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D30" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E30" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F30" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1586,36 +1841,44 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H30" s="3" t="inlineStr">
+      <c r="H30" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I30" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>1 km Repeats</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B31" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr"/>
-      <c r="E31" s="4" t="inlineStr"/>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="C31" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1625,71 +1888,87 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H31" s="3" t="inlineStr">
+      <c r="H31" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I31" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>30:30 Hard Intermittent</t>
         </is>
       </c>
-      <c r="B32" s="3" t="inlineStr">
+      <c r="B32" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C32" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr"/>
-      <c r="E32" s="4" t="inlineStr"/>
-      <c r="F32" s="4" t="inlineStr">
+      <c r="C32" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H32" s="3" t="inlineStr"/>
-      <c r="I32" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H32" s="9" t="inlineStr"/>
+      <c r="I32" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>400 m Repeats</t>
         </is>
       </c>
-      <c r="B33" s="3" t="inlineStr">
+      <c r="B33" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C33" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr"/>
-      <c r="E33" s="4" t="inlineStr"/>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="C33" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F33" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1699,71 +1978,87 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H33" s="3" t="inlineStr">
+      <c r="H33" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I33" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I33" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>Classic 4×4</t>
         </is>
       </c>
-      <c r="B34" s="3" t="inlineStr">
+      <c r="B34" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C34" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr"/>
-      <c r="E34" s="4" t="inlineStr"/>
-      <c r="F34" s="4" t="inlineStr">
+      <c r="C34" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F34" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H34" s="9" t="inlineStr"/>
+      <c r="I34" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>Footy Shuttles</t>
         </is>
       </c>
-      <c r="B35" s="3" t="inlineStr">
+      <c r="B35" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C35" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr"/>
-      <c r="E35" s="4" t="inlineStr"/>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E35" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F35" s="10" t="inlineStr">
         <is>
           <t>one_plus_years</t>
         </is>
@@ -1773,679 +2068,831 @@
           <t>⚑ field sprint at top-end speed. Gate here is conditioning base, not lifting experience, so this ladder may not be the right instrument at all.</t>
         </is>
       </c>
-      <c r="H35" s="3" t="inlineStr">
+      <c r="H35" s="9" t="inlineStr">
         <is>
           <t>⚑</t>
         </is>
       </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+      <c r="I35" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Three-Minute Intervals</t>
         </is>
       </c>
-      <c r="B36" s="3" t="inlineStr">
+      <c r="B36" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr"/>
-      <c r="E36" s="4" t="inlineStr"/>
-      <c r="F36" s="4" t="inlineStr">
+      <c r="C36" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H36" s="9" t="inlineStr"/>
+      <c r="I36" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>Two-Minute Repeats</t>
         </is>
       </c>
-      <c r="B37" s="3" t="inlineStr">
+      <c r="B37" s="9" t="inlineStr">
         <is>
           <t>aerobic_power</t>
         </is>
       </c>
-      <c r="C37" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr"/>
-      <c r="E37" s="4" t="inlineStr"/>
-      <c r="F37" s="4" t="inlineStr">
+      <c r="C37" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>erg-only — hard, but mechanically safe.</t>
-        </is>
-      </c>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>erg-only — hard, but mechanically safe. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H37" s="9" t="inlineStr"/>
+      <c r="I37" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>1 min On / 1 min Easy Tempo</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr">
+      <c r="B38" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr"/>
-      <c r="E38" s="4" t="inlineStr"/>
-      <c r="F38" s="4" t="inlineStr">
+      <c r="C38" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H38" s="9" t="inlineStr"/>
+      <c r="I38" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>2 min On / 1 min Easy</t>
+        </is>
+      </c>
+      <c r="B39" s="9" t="inlineStr">
+        <is>
+          <t>aerobic_capacity</t>
+        </is>
+      </c>
+      <c r="C39" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H39" s="9" t="inlineStr"/>
+      <c r="I39" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>30:30 Controlled Tempo Blocks</t>
+        </is>
+      </c>
+      <c r="B40" s="9" t="inlineStr">
+        <is>
+          <t>aerobic_capacity</t>
+        </is>
+      </c>
+      <c r="C40" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D40" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H40" s="9" t="inlineStr"/>
+      <c r="I40" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="9" t="inlineStr">
+        <is>
+          <t>Aerobic Shuttles</t>
+        </is>
+      </c>
+      <c r="B41" s="9" t="inlineStr">
+        <is>
+          <t>aerobic_capacity</t>
+        </is>
+      </c>
+      <c r="C41" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>Calves</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
           <t>aerobic intensity — no gate needed.</t>
         </is>
       </c>
-      <c r="H38" s="3" t="inlineStr"/>
-      <c r="I38" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>2 min On / 1 min Easy</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
+      <c r="H41" s="9" t="inlineStr"/>
+      <c r="I41" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>Continuous Aerobic Run</t>
+        </is>
+      </c>
+      <c r="B42" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C39" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr"/>
-      <c r="E39" s="4" t="inlineStr"/>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr"/>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>30:30 Controlled Tempo Blocks</t>
-        </is>
-      </c>
-      <c r="B40" s="3" t="inlineStr">
+      <c r="C42" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D42" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E42" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H42" s="9" t="inlineStr"/>
+      <c r="I42" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="9" t="inlineStr">
+        <is>
+          <t>Controlled 10–20 min Blocks</t>
+        </is>
+      </c>
+      <c r="B43" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr"/>
-      <c r="E40" s="4" t="inlineStr"/>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G40" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H40" s="3" t="inlineStr"/>
-      <c r="I40" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>Aerobic Shuttles</t>
-        </is>
-      </c>
-      <c r="B41" s="3" t="inlineStr">
+      <c r="C43" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D43" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E43" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H43" s="9" t="inlineStr"/>
+      <c r="I43" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="9" t="inlineStr">
+        <is>
+          <t>Extensive Tempo (100 m repeats)</t>
+        </is>
+      </c>
+      <c r="B44" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C41" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr"/>
-      <c r="E41" s="4" t="inlineStr"/>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G41" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H41" s="3" t="inlineStr"/>
-      <c r="I41" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="3" t="inlineStr">
-        <is>
-          <t>Continuous Aerobic Run</t>
-        </is>
-      </c>
-      <c r="B42" s="3" t="inlineStr">
+      <c r="C44" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D44" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E44" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F44" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H44" s="9" t="inlineStr"/>
+      <c r="I44" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="9" t="inlineStr">
+        <is>
+          <t>Long Aerobic Intervals</t>
+        </is>
+      </c>
+      <c r="B45" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C42" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr"/>
-      <c r="E42" s="4" t="inlineStr"/>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G42" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H42" s="3" t="inlineStr"/>
-      <c r="I42" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Controlled 10–20 min Blocks</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
+      <c r="C45" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D45" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H45" s="9" t="inlineStr"/>
+      <c r="I45" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="9" t="inlineStr">
+        <is>
+          <t>Steady 5 min Blocks</t>
+        </is>
+      </c>
+      <c r="B46" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C43" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D43" s="4" t="inlineStr"/>
-      <c r="E43" s="4" t="inlineStr"/>
-      <c r="F43" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G43" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="3" t="inlineStr">
-        <is>
-          <t>Extensive Tempo (100 m repeats)</t>
-        </is>
-      </c>
-      <c r="B44" s="3" t="inlineStr">
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D46" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E46" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>everyone</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr"/>
+      <c r="I46" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="9" t="inlineStr">
+        <is>
+          <t>Steady Blocks (3×8 min or 4×6 min)</t>
+        </is>
+      </c>
+      <c r="B47" s="9" t="inlineStr">
         <is>
           <t>aerobic_capacity</t>
         </is>
       </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr"/>
-      <c r="E44" s="4" t="inlineStr"/>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G44" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr"/>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>Long Aerobic Intervals</t>
-        </is>
-      </c>
-      <c r="B45" s="3" t="inlineStr">
-        <is>
-          <t>aerobic_capacity</t>
-        </is>
-      </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D45" s="4" t="inlineStr"/>
-      <c r="E45" s="4" t="inlineStr"/>
-      <c r="F45" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H45" s="3" t="inlineStr"/>
-      <c r="I45" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>Steady 5 min Blocks</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
-        <is>
-          <t>aerobic_capacity</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D46" s="4" t="inlineStr"/>
-      <c r="E46" s="4" t="inlineStr"/>
-      <c r="F46" s="4" t="inlineStr">
-        <is>
-          <t>everyone</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H46" s="3" t="inlineStr"/>
-      <c r="I46" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>Steady Blocks (3×8 min or 4×6 min)</t>
-        </is>
-      </c>
-      <c r="B47" s="3" t="inlineStr">
-        <is>
-          <t>aerobic_capacity</t>
-        </is>
-      </c>
-      <c r="C47" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr"/>
-      <c r="E47" s="4" t="inlineStr"/>
-      <c r="F47" s="4" t="inlineStr">
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D47" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>aerobic intensity — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H47" s="3" t="inlineStr"/>
-      <c r="I47" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>aerobic intensity — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr"/>
+      <c r="I47" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="9" t="inlineStr">
         <is>
           <t>Easy Aerobic Flush</t>
         </is>
       </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="B48" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D48" s="4" t="inlineStr"/>
-      <c r="E48" s="4" t="inlineStr"/>
-      <c r="F48" s="4" t="inlineStr">
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D48" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H48" s="3" t="inlineStr"/>
-      <c r="I48" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr"/>
+      <c r="I48" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="9" t="inlineStr">
         <is>
           <t>Erg Flush Blocks</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="B49" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D49" s="4" t="inlineStr"/>
-      <c r="E49" s="4" t="inlineStr"/>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="C49" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D49" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E49" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F49" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H49" s="3" t="inlineStr"/>
-      <c r="I49" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H49" s="9" t="inlineStr"/>
+      <c r="I49" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="9" t="inlineStr">
         <is>
           <t>Flush Intervals 1:1 (1 min / 1 min)</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr">
+      <c r="B50" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C50" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D50" s="4" t="inlineStr"/>
-      <c r="E50" s="4" t="inlineStr"/>
-      <c r="F50" s="4" t="inlineStr">
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D50" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E50" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F50" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H50" s="3" t="inlineStr"/>
-      <c r="I50" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H50" s="9" t="inlineStr"/>
+      <c r="I50" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="9" t="inlineStr">
         <is>
           <t>Flush Intervals 2:1 (2 min / 1 min)</t>
         </is>
       </c>
-      <c r="B51" s="3" t="inlineStr">
+      <c r="B51" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C51" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D51" s="4" t="inlineStr"/>
-      <c r="E51" s="4" t="inlineStr"/>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="C51" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D51" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E51" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F51" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H51" s="3" t="inlineStr"/>
-      <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H51" s="9" t="inlineStr"/>
+      <c r="I51" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="9" t="inlineStr">
         <is>
           <t>Flush Intervals 30:30</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr">
+      <c r="B52" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C52" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D52" s="4" t="inlineStr"/>
-      <c r="E52" s="4" t="inlineStr"/>
-      <c r="F52" s="4" t="inlineStr">
+      <c r="C52" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D52" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E52" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr"/>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H52" s="9" t="inlineStr"/>
+      <c r="I52" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>Nasal-Paced Easy</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr">
+      <c r="B53" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C53" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D53" s="4" t="inlineStr"/>
-      <c r="E53" s="4" t="inlineStr"/>
-      <c r="F53" s="4" t="inlineStr">
+      <c r="C53" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E53" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F53" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H53" s="3" t="inlineStr"/>
-      <c r="I53" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H53" s="9" t="inlineStr"/>
+      <c r="I53" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="9" t="inlineStr">
         <is>
           <t>Short Flush</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr">
+      <c r="B54" s="9" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="C54" s="3" t="inlineStr">
-        <is>
-          <t>Conditioning</t>
-        </is>
-      </c>
-      <c r="D54" s="4" t="inlineStr"/>
-      <c r="E54" s="4" t="inlineStr"/>
-      <c r="F54" s="4" t="inlineStr">
+      <c r="C54" s="9" t="inlineStr">
+        <is>
+          <t>Conditioning</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>— from map —</t>
+        </is>
+      </c>
+      <c r="F54" s="10" t="inlineStr">
         <is>
           <t>everyone</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>recovery flush — no gate needed.</t>
-        </is>
-      </c>
-      <c r="H54" s="3" t="inlineStr"/>
-      <c r="I54" s="3" t="inlineStr">
-        <is>
-          <t>PROPOSED</t>
+          <t>recovery flush — no gate needed. Muscles derive from the Modality Muscle Map tab (whichever machine renders); no per-template tag needed.</t>
+        </is>
+      </c>
+      <c r="H54" s="9" t="inlineStr"/>
+      <c r="I54" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2907,190 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="8" t="inlineStr">
+        <is>
+          <t>Modality</t>
+        </is>
+      </c>
+      <c r="B1" s="8" t="inlineStr">
+        <is>
+          <t>Primary muscle groups</t>
+        </is>
+      </c>
+      <c r="C1" s="8" t="inlineStr">
+        <is>
+          <t>Secondary muscle groups</t>
+        </is>
+      </c>
+      <c r="D1" s="2" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="E1" s="8" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Bike</t>
+        </is>
+      </c>
+      <c r="B2" s="10" t="inlineStr">
+        <is>
+          <t>Quads</t>
+        </is>
+      </c>
+      <c r="C2" s="10" t="inlineStr">
+        <is>
+          <t>Calves, Knee, Glutes</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Sam's words 2026-08-05: 'bike is quads, calves, knee'.</t>
+        </is>
+      </c>
+      <c r="E2" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="inlineStr">
+        <is>
+          <t>Air Bike</t>
+        </is>
+      </c>
+      <c r="B3" s="10" t="inlineStr">
+        <is>
+          <t>Quads</t>
+        </is>
+      </c>
+      <c r="C3" s="10" t="inlineStr">
+        <is>
+          <t>Shoulders, Triceps, Calves</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>Arms drive adds upper body over Bike.</t>
+        </is>
+      </c>
+      <c r="E3" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>Row</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Low back, Glutes, Hamstrings</t>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>Shoulders, Upper back, Grip</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Sam's words 2026-08-05: 'row is lower back, glutes, hammies, shoulders, wrist' — vocab has no Wrist; Grip is the closest signed word. Add Wrist to the vocabulary instead if you want it.</t>
+        </is>
+      </c>
+      <c r="E4" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Ski</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Lats, Triceps, Midline</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>Shoulders, Low back, Grip</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Ski erg pull-down: trunk drives every stroke (Midline primary per Sam 2026-08-05); sustained handle grip like Row.</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>Run</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="inlineStr">
+        <is>
+          <t>(per template row)</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>(per template row)</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Running load varies with the quality — top-end is hamstring-dominant, acceleration is glute/quad — so Run keeps the per-template muscles on the first tab.</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="150" customWidth="1" min="1" max="1"/>
@@ -2548,6 +3178,20 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="7" t="inlineStr">
+        <is>
+          <t>MODALITY MUSCLE MAP tab (added at Sam's direction): machine sessions carry the MACHINE's muscles, authored once per modality and derived per session at render. Run keeps per-template muscles. Edit the yellow cells there too.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>SIGNED by Sam in full, 2026-08-05 (chat ruling: "all looks good"). Every row above is now his authored word.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/MUSCLE_EXPERIENCE_CONDITIONING_PROPOSED_2026-08-05.xlsx
+++ b/docs/MUSCLE_EXPERIENCE_CONDITIONING_PROPOSED_2026-08-05.xlsx
@@ -80,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -110,6 +110,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2907,7 +2913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3053,27 +3059,54 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Mixed — rotating</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Quads, Glutes, Midline</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>Hamstrings, Calves, Shoulders, Upper back, Low back</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Sam's ruling 2026-08-05: whole-body — a rotating session loads everything; vocabulary rendering by the review seat, Sam-authorized ('3a whole-body').</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>SIGNED 2026-08-05</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Run</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>(per template row)</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>(per template row)</t>
         </is>
       </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Running load varies with the quality — top-end is hamstring-dominant, acceleration is glute/quad — so Run keeps the per-template muscles on the first tab.</t>
         </is>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>—</t>
         </is>
